--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1793,6 +1793,127 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130021515</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56921</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Märrsprängarn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>477215</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6592364</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,7 +1798,7 @@
         <v>130021515</v>
       </c>
       <c r="B12" t="n">
-        <v>56922</v>
+        <v>57007</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,6 +1913,127 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130273746</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57007</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>477322</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6592326</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -1919,7 +1919,7 @@
         <v>130273746</v>
       </c>
       <c r="B13" t="n">
-        <v>57007</v>
+        <v>57033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>130307942</v>
       </c>
       <c r="B14" t="n">
-        <v>57658</v>
+        <v>57684</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -1919,7 +1919,7 @@
         <v>130273746</v>
       </c>
       <c r="B13" t="n">
-        <v>57033</v>
+        <v>57035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>130307942</v>
       </c>
       <c r="B14" t="n">
-        <v>57684</v>
+        <v>57686</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -1919,7 +1919,7 @@
         <v>130273746</v>
       </c>
       <c r="B13" t="n">
-        <v>57035</v>
+        <v>57043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>130307942</v>
       </c>
       <c r="B14" t="n">
-        <v>57686</v>
+        <v>57694</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -2040,7 +2040,7 @@
         <v>130307942</v>
       </c>
       <c r="B14" t="n">
-        <v>57694</v>
+        <v>57695</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -2040,7 +2040,7 @@
         <v>130307942</v>
       </c>
       <c r="B14" t="n">
-        <v>57695</v>
+        <v>57696</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -2040,7 +2040,7 @@
         <v>130307942</v>
       </c>
       <c r="B14" t="n">
-        <v>57696</v>
+        <v>57710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2163,6 +2163,245 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131332987</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79245</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>477145</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6592216</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131332664</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57073</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>477194</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6592317</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Med blindtarmsutfällning -nattgrop.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -2168,7 +2168,7 @@
         <v>131332987</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -2168,7 +2168,7 @@
         <v>131332987</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>131332664</v>
       </c>
       <c r="B16" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -2168,7 +2168,7 @@
         <v>131332987</v>
       </c>
       <c r="B15" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>131332664</v>
       </c>
       <c r="B16" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -2168,7 +2168,7 @@
         <v>131332987</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122987494</v>
+        <v>122987176</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477141</v>
+        <v>477043</v>
       </c>
       <c r="R2" t="n">
-        <v>6592231</v>
+        <v>6592237</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122987487</v>
+        <v>122987502</v>
       </c>
       <c r="B3" t="n">
-        <v>78867</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,26 +788,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477142</v>
+        <v>477085</v>
       </c>
       <c r="R3" t="n">
-        <v>6592232</v>
+        <v>6592365</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122987502</v>
+        <v>127700325</v>
       </c>
       <c r="B4" t="n">
-        <v>96929</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,23 +908,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Märrsprängardrågen, Vrm</t>
+          <t>Märrsprängaren, Märrsprängaren, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477085</v>
+        <v>477073</v>
       </c>
       <c r="R4" t="n">
-        <v>6592365</v>
+        <v>6592330</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,12 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,34 +968,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122987308</v>
+        <v>127716154</v>
       </c>
       <c r="B5" t="n">
-        <v>74814</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,40 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Märrsprängardrågen, Vrm</t>
+          <t>Märrsprängaren, Märrsprängaren, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477059</v>
+        <v>477082</v>
       </c>
       <c r="R5" t="n">
-        <v>6592241</v>
+        <v>6592252</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,12 +1051,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,76 +1075,69 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700271</v>
+        <v>121756948</v>
       </c>
       <c r="B6" t="n">
-        <v>57844</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Märrsprängaren, Märrsprängaren, Vrm</t>
+          <t>Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477083</v>
+        <v>477272</v>
       </c>
       <c r="R6" t="n">
-        <v>6592331</v>
+        <v>6592291</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1174,27 +1161,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I sumpskogskant.</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,66 +1175,70 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700325</v>
+        <v>122987494</v>
       </c>
       <c r="B7" t="n">
-        <v>97117</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Märrsprängaren, Märrsprängaren, Vrm</t>
+          <t>Märrsprängardrågen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477073</v>
+        <v>477141</v>
       </c>
       <c r="R7" t="n">
-        <v>6592330</v>
+        <v>6592231</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1286,22 +1262,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,50 +1276,51 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127716154</v>
+        <v>127715977</v>
       </c>
       <c r="B8" t="n">
-        <v>97117</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477082</v>
+        <v>477118</v>
       </c>
       <c r="R8" t="n">
-        <v>6592252</v>
+        <v>6592280</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1365,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1408,7 +1375,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,59 +1402,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127715543</v>
+        <v>129479753</v>
       </c>
       <c r="B9" t="n">
-        <v>56866</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Märrsprängaren, Lobergs-omr, N Kga, Vrm</t>
+          <t>Märrsprängaren, Märrsprängaren, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477171</v>
+        <v>477149</v>
       </c>
       <c r="R9" t="n">
-        <v>6592338</v>
+        <v>6592284</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,22 +1467,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,14 +1509,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127715977</v>
+        <v>129479857</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1587,14 +1540,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Märrsprängaren, Märrsprängaren, Vrm</t>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477118</v>
+        <v>477168</v>
       </c>
       <c r="R10" t="n">
-        <v>6592280</v>
+        <v>6592263</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,22 +1574,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,65 +1616,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129482751</v>
+        <v>131332987</v>
       </c>
       <c r="B11" t="n">
-        <v>57896</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477237</v>
+        <v>477145</v>
       </c>
       <c r="R11" t="n">
-        <v>6592311</v>
+        <v>6592216</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,27 +1681,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Med andra mesar.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130021515</v>
+        <v>122987308</v>
       </c>
       <c r="B12" t="n">
-        <v>57007</v>
+        <v>75428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,61 +1734,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Märrsprängarn, Vrm</t>
+          <t>Märrsprängardrågen, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477215</v>
+        <v>477059</v>
       </c>
       <c r="R12" t="n">
-        <v>6592364</v>
+        <v>6592241</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1884,12 +1791,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,6 +1805,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1916,10 +1824,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130273746</v>
+        <v>122987487</v>
       </c>
       <c r="B13" t="n">
-        <v>57043</v>
+        <v>79413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,51 +1835,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6450</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+          <t>Märrsprängardrågen, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477322</v>
+        <v>477142</v>
       </c>
       <c r="R13" t="n">
-        <v>6592326</v>
+        <v>6592232</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,22 +1892,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,28 +1906,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130307942</v>
+        <v>127700514</v>
       </c>
       <c r="B14" t="n">
-        <v>57710</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,21 +1936,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102622</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2070,28 +1958,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Vrm</t>
+          <t>Märrsprängaren, Märrsprängaren, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477219</v>
+        <v>477039</v>
       </c>
       <c r="R14" t="n">
-        <v>6592318</v>
+        <v>6592265</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,27 +1999,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Kontakläte hona.</t>
+          <t>Tappade dun i blåbärsris.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,45 +2046,59 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131332987</v>
+        <v>127700981</v>
       </c>
       <c r="B15" t="n">
-        <v>79266</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+          <t>Märrsprängaren, Märrsprängaren, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477145</v>
+        <v>477025</v>
       </c>
       <c r="R15" t="n">
-        <v>6592216</v>
+        <v>6592180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2230,22 +2125,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Nyligen använd sandbadgrop i gammal rotvälta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,7 +2175,7 @@
         <v>131332664</v>
       </c>
       <c r="B16" t="n">
-        <v>57092</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2401,6 +2301,1003 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127715543</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Märrsprängaren, Lobergs-omr, N Kga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>477171</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6592338</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129482344</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>477243</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6592288</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130021515</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Märrsprängarn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>477215</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6592364</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130273746</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>477322</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6592326</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131334799</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>477212</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6592292</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Grop i snötäcket.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130307942</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57785</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>477219</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6592318</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Kontakläte hona.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127700271</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Märrsprängaren, Märrsprängaren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>477083</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6592331</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>I sumpskogskant.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129482751</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>477237</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6592311</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Med andra mesar.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122987176</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122987502</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700325</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127716154</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121756948</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122987494</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127715977</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129479753</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129479857</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1720,6 +1770,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131332987</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1821,6 +1876,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122987308</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1922,6 +1982,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122987487</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2043,6 +2108,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700514</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2169,6 +2239,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700981</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2301,6 +2376,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131332664</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2422,6 +2502,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127715543</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2549,6 +2634,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129482344</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2670,6 +2760,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021515</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2791,6 +2886,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130273746</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2917,6 +3017,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131334799</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3045,6 +3150,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307942</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3166,6 +3276,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700271</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3298,8 +3413,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129482751</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>